--- a/tests/fixtures/documents/budget.xlsx
+++ b/tests/fixtures/documents/budget.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Budget" sheetId="1" r:id="rId1"/>
+    <sheet name="Supplies" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -10,16 +10,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>Item</t>
+    <t>Part</t>
   </si>
   <si>
-    <t>Cost</t>
+    <t>Price</t>
   </si>
   <si>
-    <t>Lantern</t>
+    <t>Rope</t>
   </si>
   <si>
-    <t>Due</t>
+    <t>Ordered</t>
   </si>
 </sst>
 </file>
@@ -45,7 +45,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -69,10 +69,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1">
-        <v>45292</v>
+        <v>46000.25</v>
       </c>
     </row>
   </sheetData>
